--- a/data/trans_dic/P19C05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,33; 17,3</t>
+          <t>10,51; 17,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 15,44</t>
+          <t>8,59; 15,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,8</t>
+          <t>4,93; 10,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,72</t>
+          <t>6,37; 10,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 17,65</t>
+          <t>9,5; 17,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,52</t>
+          <t>4,87; 11,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,88</t>
+          <t>5,93; 13,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,31</t>
+          <t>5,55; 9,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,89; 16,48</t>
+          <t>10,88; 16,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 12,58</t>
+          <t>7,66; 12,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,69</t>
+          <t>5,98; 10,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,52</t>
+          <t>6,47; 9,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 16,73</t>
+          <t>9,27; 16,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 20,92</t>
+          <t>12,52; 20,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,18</t>
+          <t>7,0; 14,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 14,76</t>
+          <t>8,97; 14,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 11,23</t>
+          <t>5,05; 10,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,62</t>
+          <t>5,55; 11,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,93</t>
+          <t>4,12; 10,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,29</t>
+          <t>5,09; 9,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 12,54</t>
+          <t>7,81; 12,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 15,98</t>
+          <t>10,19; 15,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,7</t>
+          <t>6,41; 10,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,61</t>
+          <t>7,8; 11,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,96; 16,36</t>
+          <t>9,58; 15,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 18,76</t>
+          <t>12,13; 18,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,12; 19,46</t>
+          <t>11,96; 19,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,42</t>
+          <t>2,48; 13,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 16,07</t>
+          <t>5,33; 14,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 29,17</t>
+          <t>17,52; 28,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 24,03</t>
+          <t>10,17; 23,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,79; 20,96</t>
+          <t>11,59; 20,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 14,77</t>
+          <t>9,64; 14,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,7; 20,36</t>
+          <t>14,81; 20,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,56; 19,2</t>
+          <t>12,47; 19,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 14,24</t>
+          <t>3,78; 14,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,6; 20,61</t>
+          <t>15,62; 20,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 19,06</t>
+          <t>14,2; 18,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,32</t>
+          <t>9,94; 14,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,68</t>
+          <t>10,62; 14,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 16,52</t>
+          <t>11,19; 16,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 16,14</t>
+          <t>10,99; 16,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,07</t>
+          <t>5,86; 10,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,02</t>
+          <t>3,76; 9,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 18,21</t>
+          <t>14,43; 18,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 17,24</t>
+          <t>13,66; 17,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,9</t>
+          <t>8,79; 12,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,73</t>
+          <t>7,27; 11,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 15,48</t>
+          <t>7,43; 15,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,13; 22,88</t>
+          <t>15,24; 23,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 13,24</t>
+          <t>7,44; 13,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 11,36</t>
+          <t>6,59; 11,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,04; 19,73</t>
+          <t>12,66; 19,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,43; 27,75</t>
+          <t>21,22; 28,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 17,28</t>
+          <t>11,11; 17,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 15,48</t>
+          <t>9,26; 15,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 17,24</t>
+          <t>11,9; 17,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,68; 25,0</t>
+          <t>19,72; 24,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,7</t>
+          <t>10,42; 14,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 13,19</t>
+          <t>9,45; 13,43</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,56</t>
+          <t>0,42; 3,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 7,1</t>
+          <t>2,12; 7,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,32</t>
+          <t>2,07; 7,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,86</t>
+          <t>0,48; 6,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 24,91</t>
+          <t>19,9; 25,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,94; 25,67</t>
+          <t>19,77; 25,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,84; 18,07</t>
+          <t>12,55; 18,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,25</t>
+          <t>15,08; 19,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,45; 20,92</t>
+          <t>16,12; 20,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,51; 21,62</t>
+          <t>16,84; 21,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,92; 15,16</t>
+          <t>10,71; 14,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 15,4</t>
+          <t>11,7; 15,49</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 15,07</t>
+          <t>12,3; 14,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,6; 16,48</t>
+          <t>13,55; 16,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,57; 11,96</t>
+          <t>9,51; 11,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,89</t>
+          <t>7,31; 10,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,77; 17,61</t>
+          <t>14,75; 17,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,86; 19,62</t>
+          <t>16,68; 19,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,32; 12,88</t>
+          <t>10,33; 12,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,82; 12,26</t>
+          <t>8,96; 12,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,93; 15,94</t>
+          <t>13,96; 15,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,65; 17,62</t>
+          <t>15,72; 17,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 12,05</t>
+          <t>10,31; 12,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,92; 11,32</t>
+          <t>8,95; 11,29</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39912; 66816</t>
+          <t>40601; 69164</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33830; 61033</t>
+          <t>33977; 62325</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19123; 41867</t>
+          <t>19120; 41353</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31335; 53448</t>
+          <t>31748; 54349</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25479; 47358</t>
+          <t>25485; 48081</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13689; 33874</t>
+          <t>14311; 34660</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18697; 40689</t>
+          <t>18738; 41539</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23745; 41049</t>
+          <t>24493; 42223</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71294; 107881</t>
+          <t>71227; 107222</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54059; 86707</t>
+          <t>52793; 88810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43629; 75207</t>
+          <t>42037; 72826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60038; 89450</t>
+          <t>60772; 88289</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27434; 50210</t>
+          <t>27839; 50433</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49585; 80270</t>
+          <t>48041; 80409</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21876; 44897</t>
+          <t>22172; 45349</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40499; 66188</t>
+          <t>40217; 65618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17291; 37463</t>
+          <t>16851; 35661</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16939; 36434</t>
+          <t>17391; 37170</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14168; 33126</t>
+          <t>13734; 33795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18989; 35092</t>
+          <t>19209; 34916</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49698; 79466</t>
+          <t>49473; 81360</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71192; 111396</t>
+          <t>71079; 107755</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40890; 69573</t>
+          <t>41677; 70390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65254; 95933</t>
+          <t>64448; 96131</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42870; 70382</t>
+          <t>41201; 68808</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63443; 100433</t>
+          <t>64943; 100829</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49117; 78857</t>
+          <t>48479; 77840</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15517; 88702</t>
+          <t>16393; 87900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7915; 22502</t>
+          <t>7472; 20828</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41263; 70194</t>
+          <t>42170; 69303</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13481; 33506</t>
+          <t>14185; 33345</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19448; 34585</t>
+          <t>19126; 34239</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54151; 84266</t>
+          <t>54980; 84730</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114123; 158014</t>
+          <t>114986; 161824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68387; 104561</t>
+          <t>67902; 104463</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34571; 117550</t>
+          <t>31203; 117569</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>135958; 179611</t>
+          <t>136119; 180161</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137169; 185425</t>
+          <t>138167; 184687</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86910; 125930</t>
+          <t>87419; 127296</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107449; 146544</t>
+          <t>105982; 146403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65654; 98521</t>
+          <t>66732; 99134</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75085; 112802</t>
+          <t>76786; 113320</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39910; 68885</t>
+          <t>40116; 69626</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38097; 96124</t>
+          <t>36087; 95770</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>210380; 267197</t>
+          <t>211741; 264302</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>228214; 288112</t>
+          <t>228332; 286775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>138366; 186119</t>
+          <t>137488; 188801</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>139986; 229644</t>
+          <t>142267; 228743</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18397; 38383</t>
+          <t>18412; 38332</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61026; 92287</t>
+          <t>61448; 93609</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31625; 56298</t>
+          <t>31621; 55724</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28687; 49842</t>
+          <t>28932; 50098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59476; 89984</t>
+          <t>57747; 90788</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>143516; 185847</t>
+          <t>142159; 188213</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61294; 96323</t>
+          <t>61924; 96322</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>78750; 125993</t>
+          <t>75354; 124479</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83901; 121395</t>
+          <t>83784; 121051</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>211219; 268324</t>
+          <t>211641; 266193</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101049; 144414</t>
+          <t>102349; 142192</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>119472; 165225</t>
+          <t>118385; 168276</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>880; 7556</t>
+          <t>881; 8192</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3992; 15703</t>
+          <t>4698; 16343</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4960; 17683</t>
+          <t>4994; 18809</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1470; 16001</t>
+          <t>1117; 14983</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>185714; 235555</t>
+          <t>188138; 238694</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>184529; 237566</t>
+          <t>182949; 236543</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>105954; 149110</t>
+          <t>103576; 149747</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>110013; 143220</t>
+          <t>112159; 142811</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>190464; 242279</t>
+          <t>186701; 240093</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>189338; 247922</t>
+          <t>193047; 246180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>116501; 161785</t>
+          <t>114215; 159271</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>114048; 150494</t>
+          <t>114295; 151349</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>299987; 368962</t>
+          <t>301232; 364640</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>396048; 479844</t>
+          <t>394576; 477241</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>254274; 317619</t>
+          <t>252651; 317987</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243028; 356986</t>
+          <t>239773; 354544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>404658; 482617</t>
+          <t>404203; 481332</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>529892; 616452</t>
+          <t>524183; 614015</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>294580; 367803</t>
+          <t>294948; 366847</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>308800; 429117</t>
+          <t>313641; 431111</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>722945; 826953</t>
+          <t>724334; 827524</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>947534; 1066624</t>
+          <t>952000; 1068701</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>566936; 664022</t>
+          <t>568321; 666142</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>604277; 767080</t>
+          <t>606909; 764916</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,9</t>
+          <t>10,44; 17,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 15,76</t>
+          <t>8,39; 15,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,67</t>
+          <t>4,91; 10,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,9</t>
+          <t>6,52; 10,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 17,92</t>
+          <t>9,65; 18,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,79</t>
+          <t>5,14; 12,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,15</t>
+          <t>6,13; 13,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,58</t>
+          <t>5,53; 9,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,38</t>
+          <t>10,93; 16,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,88</t>
+          <t>7,64; 12,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 10,35</t>
+          <t>6,22; 10,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,4</t>
+          <t>6,5; 9,42</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,8</t>
+          <t>9,1; 16,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 20,95</t>
+          <t>12,64; 20,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 14,32</t>
+          <t>7,24; 14,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,63</t>
+          <t>8,97; 14,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 10,69</t>
+          <t>5,28; 11,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,86</t>
+          <t>5,44; 11,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,13</t>
+          <t>4,17; 10,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,25</t>
+          <t>5,11; 9,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 12,84</t>
+          <t>7,78; 12,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,45</t>
+          <t>9,98; 15,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,83</t>
+          <t>6,32; 11,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 11,64</t>
+          <t>7,68; 11,22</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 15,99</t>
+          <t>9,54; 16,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,13; 18,83</t>
+          <t>12,17; 18,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 19,21</t>
+          <t>12,01; 19,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,3</t>
+          <t>9,4; 15,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,87</t>
+          <t>5,36; 15,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 28,8</t>
+          <t>17,12; 28,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,17; 23,92</t>
+          <t>9,83; 23,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 20,76</t>
+          <t>12,07; 21,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 14,86</t>
+          <t>9,6; 14,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,81; 20,85</t>
+          <t>14,87; 20,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 19,18</t>
+          <t>12,45; 18,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,24</t>
+          <t>10,87; 15,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 20,67</t>
+          <t>15,38; 20,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,2; 18,99</t>
+          <t>14,36; 19,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,47</t>
+          <t>9,91; 14,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 14,67</t>
+          <t>11,14; 15,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,63</t>
+          <t>11,24; 16,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 16,21</t>
+          <t>11,13; 16,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,18</t>
+          <t>5,75; 9,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,99</t>
+          <t>7,8; 10,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,01</t>
+          <t>14,41; 18,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 17,16</t>
+          <t>13,54; 17,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 12,08</t>
+          <t>8,68; 11,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,69</t>
+          <t>10,02; 12,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 15,46</t>
+          <t>7,74; 15,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,24; 23,21</t>
+          <t>15,26; 23,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 13,11</t>
+          <t>7,34; 13,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,42</t>
+          <t>6,12; 10,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 19,91</t>
+          <t>12,79; 19,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,22; 28,1</t>
+          <t>21,35; 28,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,28</t>
+          <t>11,26; 17,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 15,29</t>
+          <t>12,85; 16,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,9; 17,19</t>
+          <t>12,03; 17,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,72; 24,81</t>
+          <t>19,97; 24,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,42; 14,47</t>
+          <t>10,28; 14,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 13,43</t>
+          <t>10,62; 13,75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,86</t>
+          <t>0,42; 3,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,39</t>
+          <t>2,1; 7,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,79</t>
+          <t>1,99; 7,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,42</t>
+          <t>0,67; 7,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,9; 25,24</t>
+          <t>19,69; 25,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,77; 25,56</t>
+          <t>19,91; 25,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 18,14</t>
+          <t>12,94; 18,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,08; 19,2</t>
+          <t>14,88; 19,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,12; 20,74</t>
+          <t>16,37; 20,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,84; 21,47</t>
+          <t>16,69; 21,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,93</t>
+          <t>10,73; 15,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 15,49</t>
+          <t>12,18; 15,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,3; 14,89</t>
+          <t>12,24; 14,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,55; 16,39</t>
+          <t>13,51; 16,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 11,97</t>
+          <t>9,47; 11,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,82</t>
+          <t>9,44; 11,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,75; 17,57</t>
+          <t>14,68; 17,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,68; 19,54</t>
+          <t>16,86; 19,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,33; 12,85</t>
+          <t>10,39; 12,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,96; 12,32</t>
+          <t>11,21; 12,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,96; 15,95</t>
+          <t>13,95; 15,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,72; 17,65</t>
+          <t>15,61; 17,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,31; 12,09</t>
+          <t>10,26; 12,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,95; 11,29</t>
+          <t>10,61; 11,96</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41394</t>
+          <t>45849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>34393</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73484</t>
+          <t>80242</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40601; 69164</t>
+          <t>40314; 67497</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33977; 62325</t>
+          <t>33178; 61693</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19120; 41353</t>
+          <t>19036; 41792</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31748; 54349</t>
+          <t>35301; 58606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25485; 48081</t>
+          <t>25878; 48836</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14311; 34660</t>
+          <t>15101; 35304</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18738; 41539</t>
+          <t>19358; 42401</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24493; 42223</t>
+          <t>26610; 44539</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71227; 107222</t>
+          <t>71514; 108443</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52793; 88810</t>
+          <t>52672; 86404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42037; 72826</t>
+          <t>43734; 74763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60772; 88289</t>
+          <t>66438; 96354</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51961</t>
+          <t>54945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78601</t>
+          <t>83970</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27839; 50433</t>
+          <t>27317; 50669</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48041; 80409</t>
+          <t>48499; 79962</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22172; 45349</t>
+          <t>22926; 46076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40217; 65618</t>
+          <t>42986; 68768</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16851; 35661</t>
+          <t>17611; 37244</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17391; 37170</t>
+          <t>17045; 37357</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13734; 33795</t>
+          <t>13917; 33344</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19209; 34916</t>
+          <t>21345; 38374</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49473; 81360</t>
+          <t>49295; 79723</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71079; 107755</t>
+          <t>69601; 111037</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41677; 70390</t>
+          <t>41124; 71537</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64448; 96131</t>
+          <t>68890; 100658</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51341</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>85507</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41201; 68808</t>
+          <t>41066; 68949</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64943; 100829</t>
+          <t>65161; 100049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48479; 77840</t>
+          <t>48663; 78614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16393; 87900</t>
+          <t>43609; 69611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7472; 20828</t>
+          <t>7508; 21721</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42170; 69303</t>
+          <t>41195; 68674</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14185; 33345</t>
+          <t>13701; 32911</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19126; 34239</t>
+          <t>22309; 39616</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54980; 84730</t>
+          <t>54745; 83760</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114986; 161824</t>
+          <t>115399; 158414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67902; 104463</t>
+          <t>67783; 103204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31203; 117569</t>
+          <t>70524; 102982</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>71340</t>
+          <t>77870</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>196487</t>
+          <t>219864</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>136119; 180161</t>
+          <t>134044; 177388</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138167; 184687</t>
+          <t>139692; 184926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87419; 127296</t>
+          <t>87148; 127187</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105982; 146403</t>
+          <t>122032; 165538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66732; 99134</t>
+          <t>66991; 99401</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76786; 113320</t>
+          <t>77799; 116267</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40116; 69626</t>
+          <t>39341; 68271</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36087; 95770</t>
+          <t>65301; 91879</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>211741; 264302</t>
+          <t>211540; 266185</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>228332; 286775</t>
+          <t>226367; 288526</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>137488; 188801</t>
+          <t>135640; 184574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>142267; 228743</t>
+          <t>193548; 245368</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>105788</t>
+          <t>116533</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>144581</t>
+          <t>157362</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18412; 38332</t>
+          <t>19197; 38125</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61448; 93609</t>
+          <t>61549; 94082</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31621; 55724</t>
+          <t>31189; 56359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28932; 50098</t>
+          <t>31195; 52721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57747; 90788</t>
+          <t>58327; 90708</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>142159; 188213</t>
+          <t>143009; 189826</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61924; 96322</t>
+          <t>62754; 97130</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>75354; 124479</t>
+          <t>101927; 133397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83784; 121051</t>
+          <t>84673; 123679</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>211641; 266193</t>
+          <t>214343; 267669</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102349; 142192</t>
+          <t>101001; 143240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>118385; 168276</t>
+          <t>138378; 179191</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>138641</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>131533</t>
+          <t>144375</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>881; 8192</t>
+          <t>883; 7452</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4698; 16343</t>
+          <t>4655; 15646</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4994; 18809</t>
+          <t>4815; 17890</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1117; 14983</t>
+          <t>1509; 16254</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>188138; 238694</t>
+          <t>186203; 241055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>182949; 236543</t>
+          <t>184262; 239009</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>103576; 149747</t>
+          <t>106807; 150721</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>112159; 142811</t>
+          <t>121839; 157002</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>186701; 240093</t>
+          <t>189580; 242115</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>193047; 246180</t>
+          <t>191364; 245520</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114215; 159271</t>
+          <t>114462; 160861</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>114295; 151349</t>
+          <t>127219; 166325</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>314097</t>
+          <t>345259</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>388211</t>
+          <t>426063</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>702308</t>
+          <t>771321</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>301232; 364640</t>
+          <t>299802; 366717</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>394576; 477241</t>
+          <t>393451; 478079</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>252651; 317987</t>
+          <t>251618; 315755</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>239773; 354544</t>
+          <t>312967; 382871</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>404203; 481332</t>
+          <t>402234; 482374</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>524183; 614015</t>
+          <t>529692; 617949</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>294948; 366847</t>
+          <t>296792; 370391</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>313641; 431111</t>
+          <t>396192; 456931</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>724334; 827524</t>
+          <t>723635; 828223</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>952000; 1068701</t>
+          <t>944871; 1064025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>568321; 666142</t>
+          <t>565712; 663954</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>606909; 764916</t>
+          <t>726442; 818958</t>
         </is>
       </c>
     </row>
